--- a/public/fun/pack/xlsx/saving/저축플래너_30_은퇴후생활준비_단풍든우체통.xlsx
+++ b/public/fun/pack/xlsx/saving/저축플래너_30_은퇴후생활준비_단풍든우체통.xlsx
@@ -31,7 +31,7 @@
     <t>은퇴 후 생활 준비 저축 플래너</t>
   </si>
   <si>
-    <t>“붉게 물든 약속을 우체통에 넣어요”</t>
+    <t>“자동이체 날짜를 정리해 둡니다”</t>
   </si>
   <si>
     <t>단풍 든 우체통 테마</t>

--- a/public/fun/pack/xlsx/saving/저축플래너_30_은퇴후생활준비_단풍든우체통.xlsx
+++ b/public/fun/pack/xlsx/saving/저축플래너_30_은퇴후생활준비_단풍든우체통.xlsx
@@ -26,12 +26,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>은퇴 후 생활 준비 저축 플래너</t>
-  </si>
-  <si>
-    <t>“자동이체 날짜를 정리해 둡니다”</t>
   </si>
   <si>
     <t>단풍 든 우체통 테마</t>
@@ -1720,65 +1717,63 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="2:3" ht="6" customHeight="1"/>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="5"/>
     </row>
     <row r="7" spans="2:3" ht="32" customHeight="1">
       <c r="B7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>4</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="32" customHeight="1">
       <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="32" customHeight="1">
       <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="32" customHeight="1">
       <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="28" customHeight="1">
       <c r="B12" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="8"/>
     </row>
     <row r="14" spans="2:3">
       <c r="B14" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="9"/>
     </row>
@@ -1822,9 +1817,7 @@
       <c r="F1" s="10"/>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1832,23 +1825,23 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="11"/>
       <c r="E3" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="11"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>16</v>
-      </c>
       <c r="E4" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="14">
         <f>Monthly*Months</f>
@@ -1857,13 +1850,13 @@
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="15">
         <v>40200000</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="14">
         <f>IF(Mode="단리",Monthly*(Rate/12)*Months*(Months+1)/2,FV(Rate/12,Months,-Monthly,0,1)-Monthly*Months)</f>
@@ -1872,13 +1865,13 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="16">
         <v>46023</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" s="14">
         <f>F5*Tax</f>
@@ -1887,13 +1880,13 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="15">
         <v>650000</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="14">
         <f>F5-F6</f>
@@ -1902,13 +1895,13 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="17">
         <v>0.036</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="18">
         <f>F4+F7</f>
@@ -1917,13 +1910,13 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="19">
         <v>60</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="20">
         <f>EDATE(StartDate,Months)</f>
@@ -1932,13 +1925,13 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="E10" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10" s="21">
         <f>IF(Goal=0,0,F8/Goal)</f>
@@ -1947,13 +1940,13 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="17">
         <v>0.154</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" s="14">
         <f>MAX(0,Goal-F8)</f>
@@ -1962,7 +1955,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="E12" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" s="14">
         <f>IF(Mode="단리",Goal/(Months+(Rate/12)*(1-Tax)*Months*(Months+1)/2),IF(Rate=0,Goal/Months,Goal/(Months+(FV(Rate/12,Months,-1,0,1)-Months)*(1-Tax))))</f>
@@ -1971,7 +1964,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -2088,7 +2081,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -2102,7 +2095,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2116,34 +2109,34 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">

--- a/public/fun/pack/xlsx/saving/저축플래너_30_은퇴후생활준비_단풍든우체통.xlsx
+++ b/public/fun/pack/xlsx/saving/저축플래너_30_은퇴후생활준비_단풍든우체통.xlsx
@@ -64,7 +64,7 @@
     <t>이 표는 스스로 계획을 세우는 계산 도구이며 특정 상품의 수익을 보장하거나 권유하지 않아요. 실제 이자와 세금은 상품과 세법에 따라 달라질 수 있어요.</t>
   </si>
   <si>
-    <t>우체국보험 상담 안내 · 자유롭게 고쳐 쓰세요</t>
+    <t>반딧불이의 곳간 · 자유롭게 고쳐 쓰세요</t>
   </si>
   <si>
     <t>입력 칸</t>
@@ -178,7 +178,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="m&quot;월&quot; d&quot;일&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0&quot;개월&quot;"/>
     <numFmt numFmtId="168" formatCode="+#,##0;[Red]-#,##0;0"/>
